--- a/quizzes/017_sacraments_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/017_sacraments_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sacraments_knowledge_quiz</t>
+          <t>first_sacrament</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sacraments_knowledge_quiz</t>
+          <t>First Sacrament</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sacrament_of_baptism</t>
+          <t>sacrament_of_confession</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sacrament_of_baptism</t>
+          <t>Sacrament of Confession</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sacrament_of_confession</t>
+          <t>purpose_of_confirmation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sacrament_of_confession</t>
+          <t>Purpose of Confirmation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,81 +589,81 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sacrament_of_anointing</t>
+          <t>number_of_sacraments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sacrament_of_anointing</t>
+          <t>Number of Sacraments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sacrament_of_annointing</t>
+          <t>eucharist_sacrament</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sacrament_of_annointing</t>
+          <t>Eucharist Sacrament</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sacrament_of_confirmation</t>
+          <t>baptism_initiation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sacrament_of_confirmation</t>
+          <t>Baptism Initiation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainment</t>
+          <t>sacrament_of_reconciliation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainment</t>
+          <t>Sacrament of Reconciliation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainement</t>
+          <t>eucharist_effect</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainement</t>
+          <t>Eucharist Effect</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sacrament_of_ordianment</t>
+          <t>non_sacrament</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sacrament_of_ordianment</t>
+          <t>Non Sacrament</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sacrament_of_ordaine</t>
+          <t>anointing_sacrament</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sacrament_of_ordaine</t>
+          <t>Anointing Sacrament</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sacrament_of_ordain</t>
+          <t>matrimony_sacrament</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sacrament_of_ordain</t>
+          <t>Matrimony Sacrament</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainement</t>
+          <t>passage_sacrament</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainement</t>
+          <t>Passage Sacrament</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sacrament_of_ordain</t>
+          <t>baptism_eucharist_order</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sacrament_of_ordain</t>
+          <t>Baptism Eucharist Order</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,23 +814,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sacrament_of_ordaine</t>
+          <t>healing_sacrament</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sacrament_of_ordaine</t>
+          <t>Healing Sacrament</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainment</t>
+          <t>ordainment_sacrament</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sacrament_of_ordainment</t>
+          <t>Ordainment Sacrament</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eucharist_knowledge</t>
+          <t>ordainment_order</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>eucharist_knowledge</t>
+          <t>Ordainment Order</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sacrament_of_confession_knowlege</t>
+          <t>baptism_effect</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sacrament_of_confession_knowlege</t>
+          <t>Baptism Effect</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eucharist_knowledge</t>
+          <t>penance_sacrament</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eucharist_knowledge</t>
+          <t>Penance Sacrament</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>knowledge_of_ordainment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>knowledge_of_ordainment</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ordainment_knowledge</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ordainment_knowledge</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>knowledge_of_eucharist</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>knowledge_of_eucharist</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>understanding_of_ordaine</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>understanding_of_ordaine</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>knowledge_of_ordain</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>knowledge_of_ordain</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>knowledge_of_ordainement</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>knowledge_of_ordainement</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>eucharist_understanding</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>eucharist_understanding</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sacrament_of_baptism_choices</t>
+          <t>sacrament_of_confession_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sacrament_of_baptism_choices</t>
+          <t>sacrament_of_confession_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sacrament_of_confession_choices</t>
+          <t>eucharist_sacrament_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sacrament_of_confession_choices</t>
+          <t>eucharist_sacrament_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sacrament_of_confirmation_choices</t>
+          <t>sacrament_of_reconciliation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sacrament_of_confirmation_choices</t>
+          <t>sacrament_of_reconciliation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eucharist_knowledge_choices</t>
+          <t>non_sacrament_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eucharist_knowledge_choices</t>
+          <t>non_sacrament_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eucharist_understanding_choices</t>
+          <t>passage_sacrament_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eucharist_understanding_choices</t>
+          <t>passage_sacrament_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1288,6 +1127,108 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>healing_sacrament_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>healing_sacrament_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ordainment_order_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ordainment_order_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>penance_sacrament_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>penance_sacrament_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
